--- a/cypress/downloads/Student_Summary.xlsx
+++ b/cypress/downloads/Student_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -62,6 +62,72 @@
   </x:si>
   <x:si>
     <x:t>Agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new chil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new child</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new secondary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bsic level</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Start</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/08/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>False</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Medium</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new partner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Conditional Offer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/01/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>secondary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic level</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Applied</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/05/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mawaz Ejaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/09/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husbandmain husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husband</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -125,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P2" totalsRowShown="0">
-  <x:autoFilter ref="A1:P2"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P7" totalsRowShown="0">
+  <x:autoFilter ref="A1:P7"/>
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="EZM ID"/>
@@ -437,7 +503,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P3"/>
+  <x:dimension ref="A1:P7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -488,6 +554,159 @@
       </x:c>
       <x:c r="P1" s="0" t="s">
         <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:16">
+      <x:c r="A2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:16">
+      <x:c r="A3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:16">
+      <x:c r="A4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:16">
+      <x:c r="A5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:16">
+      <x:c r="A6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:16">
+      <x:c r="A7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Student_Summary.xlsx
+++ b/cypress/downloads/Student_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -62,72 +62,6 @@
   </x:si>
   <x:si>
     <x:t>Agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>High</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new chil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new child</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new secondary</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bsic level</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Start</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/08/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>False</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Medium</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new partner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Conditional Offer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30/01/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nimal test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>secondary</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic level</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Applied</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/05/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mawaz Ejaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/09/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>main husbandmain husband</x:t>
-  </x:si>
-  <x:si>
-    <x:t>main husband</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -191,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P7" totalsRowShown="0">
-  <x:autoFilter ref="A1:P7"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P2" totalsRowShown="0">
+  <x:autoFilter ref="A1:P2"/>
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="EZM ID"/>
@@ -503,7 +437,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P7"/>
+  <x:dimension ref="A1:P3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -554,159 +488,6 @@
       </x:c>
       <x:c r="P1" s="0" t="s">
         <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:16">
-      <x:c r="A2" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:16">
-      <x:c r="A3" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:16">
-      <x:c r="A4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:16">
-      <x:c r="A5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:16">
-      <x:c r="A6" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:16">
-      <x:c r="A7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Student_Summary.xlsx
+++ b/cypress/downloads/Student_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -62,6 +62,66 @@
   </x:si>
   <x:si>
     <x:t>Agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>High</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TST again</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new secondary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bsic level</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Start</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/01/24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>False</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new chil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new child</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/02/24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Medium</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shcool relation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>secondary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic level</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/05/24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/01/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husbandmain husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/08/23</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -125,8 +185,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P2" totalsRowShown="0">
-  <x:autoFilter ref="A1:P2"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P6" totalsRowShown="0">
+  <x:autoFilter ref="A1:P6"/>
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="EZM ID"/>
@@ -437,7 +497,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P3"/>
+  <x:dimension ref="A1:P6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -488,6 +548,127 @@
       </x:c>
       <x:c r="P1" s="0" t="s">
         <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:16">
+      <x:c r="A2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:16">
+      <x:c r="A3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:16">
+      <x:c r="A4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:16">
+      <x:c r="A5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:16">
+      <x:c r="A6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Student_Summary.xlsx
+++ b/cypress/downloads/Student_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -122,6 +122,30 @@
   </x:si>
   <x:si>
     <x:t>01/08/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1512</x:t>
+  </x:si>
+  <x:si>
+    <x:t>finame shuja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/12/24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/12/24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1515</x:t>
+  </x:si>
+  <x:si>
+    <x:t>wife WDxxh</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -185,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P6" totalsRowShown="0">
-  <x:autoFilter ref="A1:P6"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P8" totalsRowShown="0">
+  <x:autoFilter ref="A1:P8"/>
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="EZM ID"/>
@@ -497,7 +521,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P6"/>
+  <x:dimension ref="A1:P8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -669,6 +693,76 @@
       </x:c>
       <x:c r="N6" s="0" t="s">
         <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:16">
+      <x:c r="A7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:16">
+      <x:c r="A8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P8" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Student_Summary.xlsx
+++ b/cypress/downloads/Student_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <x:si>
     <x:t>Priority</x:t>
   </x:si>
@@ -122,30 +122,6 @@
   </x:si>
   <x:si>
     <x:t>01/08/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1512</x:t>
-  </x:si>
-  <x:si>
-    <x:t>finame shuja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/12/24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/12/24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1515</x:t>
-  </x:si>
-  <x:si>
-    <x:t>wife WDxxh</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -209,8 +185,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P8" totalsRowShown="0">
-  <x:autoFilter ref="A1:P8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:P6" totalsRowShown="0">
+  <x:autoFilter ref="A1:P6"/>
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="EZM ID"/>
@@ -521,7 +497,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P8"/>
+  <x:dimension ref="A1:P6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -693,76 +669,6 @@
       </x:c>
       <x:c r="N6" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:16">
-      <x:c r="A7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:16">
-      <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
